--- a/docs/SafePic_API키_데이터_체크리스트_20260823.xlsx
+++ b/docs/SafePic_API키_데이터_체크리스트_20260823.xlsx
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>지상관측 ASOS/AWS, 레이더 합성, 천리안 위성, 지진통보, 태풍정보, 가뭄지수, 격자자료</t>
+          <t>11개만: 예특보(특보 통보문·예비특보·영향예보) / 지상관측(AWS 매시·ASOS 일자료) / 레이더 합성영상 / 천리안2A RGB / 지진통보(국내) / 태풍정보 / 융합기상(생활기상지수·가뭄지수 SPI). 나머지(해양·고층·수치·항공·세계·산업특화·지상관측 기타) 제외</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>data.go.kr 키와 별개 체계. 말씀하신 '지상·레이더·위성·지진·태풍' 카테고리가 여기</t>
+          <t>활용신청 없이 키 하나로 호출, 일 한도 마이페이지 확인(우리 ~600건/일). 5km 래스터 승격 시 "동네예보 격자 파일" 1개 추가</t>
         </is>
       </c>
     </row>

--- a/docs/SafePic_API키_데이터_체크리스트_20260823.xlsx
+++ b/docs/SafePic_API키_데이터_체크리스트_20260823.xlsx
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>★★ (관악 격자 빈 컬럼)</t>
+          <t>△ 불필요(전국 대체 있음)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>A2-2</t>
+          <t>반지하→KOSIS 인구주택총조사 읍면동, 펌프장→환경부 하수도통계, 침수→NSDI 전국</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>★★ (A5 전국화)</t>
+          <t>★★★ (전국 격자 = 시범 해제의 열쇠)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4075,6 +4075,109 @@
       </c>
       <c r="G21" s="2" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>한국·전국대체</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>KOSIS 인구주택총조사 지하(반지하) 거처 가구 — 읍면동</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>https://kosis.kr</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>반지하 비율 전국(격자 semi_basement_r 채움)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>없음(파일)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>서울 데이터 불필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>한국·전국대체</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>환경부 하수도통계 — 펌프장·우수저류시설 현황</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hasudoinfo.or.kr</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>빗물펌프장 전국</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>없음(파일)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>한국·전국</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>국가공간정보포털 침수흔적도 API</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nsdi.go.kr</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>전국 격자 생성(탭③ 시범 해제)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>NSDI 키</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
